--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:00:53+00:00</t>
+    <t>2023-06-02T12:29:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -340,7 +340,7 @@
     <t>as-codeableconcept-timed-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-codeableconcept-timed-metadata}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-codeableconcept-timed-metadata}
 </t>
   </si>
   <si>
@@ -713,7 +713,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="109.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="110.890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-codeableconcept-timed.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-codeableconcept-timed.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
